--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/ALABAMA_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/ALABAMA_2021.xlsx
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C103">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C139">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C224">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C232">
@@ -11688,7 +11688,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C630">
